--- a/important_mails_2026-07-18.xlsx
+++ b/important_mails_2026-07-18.xlsx
@@ -945,7 +945,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>KYC审核类</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -960,69 +960,21 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Sat, 11 Jul 2026 09:58:04 +0000</t>
+          <t>Mon, 13 Jul 2026 06:09:58 +0000</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+          <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>FBA reimbursement notification</t>
+          <t>【官方提示】请尽快通过您的欧洲站卖家资质KYC审核，以保证正常销售</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfillment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
-- T</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>KYC审核类</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 13 Jul 2026 06:09:58 +0000</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>【官方提示】请尽快通过您的欧洲站卖家资质KYC审核，以保证正常销售</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">账户注册
 															资质审查
@@ -1055,136 +1007,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>KYC审核类</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 11 Jul 2026 08:27:01 +0000</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Know Your Customer (KYC) verification process support</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>96
- Pending Know Your Customer (KYC) account verification
- Hello,
- We are conducting a review of your Amazon Payments Account. We need additional information or documents to continue with your account verification. In accordance with regulations, you must complete an account verification process. Please go to the Identity Information page to provide the required information or documents:
- Submit documentation
- In some cases, we will send a notification that outlines the details of the request related to your Amazon Payments account. Please check the most recent performance notifications starting with the subject [Action Required]: Performance Notifications .
- What happens next?
- Once you have provided the requested information or documents, we will continue with your account verification. Please continue to proactively check the performance notifications or emails to understand if further information or documents are needed from you.
- Once the verification is complete, you will receive a performance notification and email advising you of the result.
- We’re here to help.
- If you have any questions, you can contact us at any time via Amazon Selling Partner Support .
- For more informa</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>KYC审核类</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 11 Jul 2026 08:25:53 +0000</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>[Action Required] Information needed for your Selling on Amazon
- payment account</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96
-[Action Required] Information needed for your Selling on Amazon payment account
- [Action Required] Information needed for your Selling on Amazon payment account
- Hello,
-We are contacting you because we need additional documentation to continue with your account verification.
-Providing altered or manipulated documents may result in permanent account closure.
-What happens if I do not take action?
-You have a total of 60 days from the day when we first contacted you to take action or provide all of the requested documentation and information to complete the verification. The time that we take to review and validate the outcomes of your action or validate the information will not be counted against the 60-day threshold that you are given.
-If you do not take action or provide requested information before these 60 days, your listings and the ability to disburse funds will be temporarily deactivated until verification has been completed.
-If it has been more than 60 days since we first contacted you, your disbursements and listings might have already been deactivated and will remain deactivated until the requested information or documentation has been provided and your account has been v</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Jul 2026 15:31:53 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1204,39 +1059,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Jul 2026 15:31:22 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1256,39 +1111,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Jul 2026 15:30:38 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1305,39 +1160,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Wed, 15 Jul 2026 14:47:49 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1354,39 +1209,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Jul 2026 14:58:09 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1406,39 +1261,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Jul 2026 14:21:36 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1458,39 +1313,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Jul 2026 04:03:58 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1507,140 +1362,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 11 Jul 2026 10:36:54 +0000</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 06:06:37 +0000</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 07/11/26 10:36 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 777,67.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éx</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 11 Jul 2026 10:30:59 +0000</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
-On 07/11/26 10:30 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
- 234.81.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
-Help us improve your payment experience on Ama</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 15 Jul 2026 06:06:37 +0000</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -1659,39 +1413,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Jul 2026 11:19:50 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Global Warehousing and Distribution &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Global Warehousing and Distribution’s new China shipping options are live</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
  Choose Shanghai or Shenzhen with Free on Board support
@@ -1706,39 +1460,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Wed, 15 Jul 2026 12:22:37 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Introducing the Improved Similar Items Dashboard – Smarter Pricing Starts Now</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo]
 We're excited to announce the launch of the improved Similar Items Dashboard. It helps you understand how comparable products are priced on Amazon. Instead of spending hours on manual research, it provides quick access to Amazon data – all in one place.
@@ -1756,40 +1510,40 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Wed, 15 Jul 2026 10:17:38 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Get increased New Selection Program (2026) benefits starting July
  30</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  Effective July 30, 2026, the New Selection Program (2026) launches with increased benefits to help you launch new branded products with reduced costs and complexity while boosting early sales.
@@ -1803,39 +1557,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Jul 2026 17:10:46 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -1851,39 +1605,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Jul 2026 15:32:18 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Accelerate 2026: Sessions designed for where you are and where you’re going</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-14/7z4n1pf/6770773185/h/WdBYUGZo6UnxZlR8bvark7SKCv06gleKjoxG039m7cg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1pj/6770773185/h/WdBYUGZo6UnxZlR8bvark7SKCv06gleKjoxG039m7cg)
@@ -1895,39 +1649,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Jul 2026 15:11:01 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Your Accelerate 2026 session catalog is now live</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-14/7z4n1s7/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1sb/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk)
@@ -1939,39 +1693,87 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 11 Jul 2026 09:58:04 +0000</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfillment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+- T</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 05:37:52 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1987,39 +1789,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 05:20:26 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2035,39 +1837,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 03:39:42 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2083,39 +1885,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 05:28:59 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (0uWEj59btv)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2135,39 +1937,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 04:32:11 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2183,39 +1985,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 09:21:14 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2231,39 +2033,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 09:24:36 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2279,39 +2081,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 04:17:03 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (go0BbIMUoR)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2331,39 +2133,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 16:27:45 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (hbXn1jQJTV)</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2388,39 +2190,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 05:07:37 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2436,39 +2238,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 08:53:34 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (j2cKowrwuw)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2488,39 +2290,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 04:56:23 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2536,39 +2338,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 23:44:37 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (H7OQM8penQ)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2593,39 +2395,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 04:56:45 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2641,39 +2443,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 14:57:16 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2694,39 +2496,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 14:55:52 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $81.22 in an attempt to settle your Amazon seller account balance.
@@ -2742,39 +2544,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 04:47:15 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2790,39 +2592,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 04:59:26 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2838,39 +2640,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 03:07:14 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (HI24ImSBWG)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2895,39 +2697,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 15:41:57 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2948,39 +2750,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 09:07:47 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Multchannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -2994,39 +2796,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 04:53:58 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3042,39 +2844,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 00:27:04 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FyqS0yVk5B)</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3099,39 +2901,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Wed, 24 Jun 2026 04:45:26 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3147,39 +2949,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 15:11:41 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3200,39 +3002,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 02:24:45 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (1M28ecQsao)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3257,39 +3059,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 06:20:20 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (9U/Ti42WHq)</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3309,39 +3111,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 04:45:03 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3357,39 +3159,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sun, 21 Jun 2026 14:27:31 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3410,39 +3212,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 15:35:08 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (hCxOB8pPpU)</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3467,39 +3269,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 15:10:33 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3520,39 +3322,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 04:41:46 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3568,39 +3370,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 14:16:06 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3621,39 +3423,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 08:10:33 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Multchannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -3667,39 +3469,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 20:47:57 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (oWLDk2Qx2d)</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3724,39 +3526,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 20:39:11 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Emm3dPMsXA)</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3781,39 +3583,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 17:59:35 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai EU,
@@ -3827,39 +3629,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 10 Jul 2026 11:11:12 +0000</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 11 Jul 2026 08:27:01 +0000</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -3876,39 +3678,136 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 11 Jul 2026 08:25:53 +0000</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>[Action Required] Information needed for your Selling on Amazon
+ payment account</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>96
+[Action Required] Information needed for your Selling on Amazon payment account
+ [Action Required] Information needed for your Selling on Amazon payment account
+ Hello,
+We are contacting you because we need additional documentation to continue with your account verification.
+Providing altered or manipulated documents may result in permanent account closure.
+What happens if I do not take action?
+You have a total of 60 days from the day when we first contacted you to take action or provide all of the requested documentation and information to complete the verification. The time that we take to review and validate the outcomes of your action or validate the information will not be counted against the 60-day threshold that you are given.
+If you do not take action or provide requested information before these 60 days, your listings and the ability to disburse funds will be temporarily deactivated until verification has been completed.
+If it has been more than 60 days since we first contacted you, your disbursements and listings might have already been deactivated and will remain deactivated until the requested information or documentation has been provided and your account has been v</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>KYC审核类</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 10 Jul 2026 11:11:12 +0000</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Know Your Customer (KYC) verification process support</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Pending Know Your Customer (KYC) account verification
+ Hello,
+ We are conducting a review of your Amazon Payments Account. We need additional information or documents to continue with your account verification. In accordance with regulations, you must complete an account verification process. Please go to the Identity Information page to provide the required information or documents:
+ Submit documentation
+ In some cases, we will send a notification that outlines the details of the request related to your Amazon Payments account. Please check the most recent performance notifications starting with the subject [Action Required]: Performance Notifications .
+ What happens next?
+ Once you have provided the requested information or documents, we will continue with your account verification. Please continue to proactively check the performance notifications or emails to understand if further information or documents are needed from you.
+ Once the verification is complete, you will receive a performance notification and email advising you of the result.
+ We’re here to help.
+ If you have any questions, you can contact us at any time via Amazon Selling Partner Support .
+ For more informa</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>KYC审核类</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 14:32:29 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Seller News: June 2026</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3922,6 +3821,107 @@
  Read more .
  New handling time requirements for seller-fulfilled products
  Fast and accurate delivery builds customer trust and is a key factor in purchase decisions. In fact, every one day improvement in promised delivery time leads to an average 5% increase in sales. As such, we’re implementing a new handling time requirem</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 11 Jul 2026 10:36:54 +0000</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Tu pago está en camino</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 07/11/26 10:36 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 777,67.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éx</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 11 Jul 2026 10:30:59 +0000</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 07/11/26 10:30 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
+ 234.81.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Ama</t>
         </is>
       </c>
     </row>
